--- a/research/traditional_assets/database/data/new_zealand/new_zealand_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1434</v>
+        <v>0.1702</v>
       </c>
       <c r="E2">
-        <v>0.09109999999999999</v>
+        <v>-0.009950000000000001</v>
       </c>
       <c r="F2">
-        <v>0.07690000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="G2">
-        <v>0.2629243917246533</v>
+        <v>0.2392880685563613</v>
       </c>
       <c r="H2">
-        <v>0.2629243917246533</v>
+        <v>0.2090592334494774</v>
       </c>
       <c r="I2">
-        <v>0.2382898239387288</v>
+        <v>0.1742160278745645</v>
       </c>
       <c r="J2">
-        <v>0.1948839365804579</v>
+        <v>0.1435084080724074</v>
       </c>
       <c r="K2">
-        <v>15.425</v>
+        <v>0.3269999999999996</v>
       </c>
       <c r="L2">
-        <v>0.1800891981506562</v>
+        <v>0.00307938600621527</v>
       </c>
       <c r="M2">
-        <v>11.21</v>
+        <v>10.94</v>
       </c>
       <c r="N2">
-        <v>0.02856924410010704</v>
+        <v>0.03638298579932821</v>
       </c>
       <c r="O2">
-        <v>0.726742301458671</v>
+        <v>33.45565749235479</v>
       </c>
       <c r="P2">
-        <v>11.21</v>
+        <v>10.94</v>
       </c>
       <c r="Q2">
-        <v>0.02856924410010704</v>
+        <v>0.03638298579932821</v>
       </c>
       <c r="R2">
-        <v>0.726742301458671</v>
+        <v>33.45565749235479</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>49.705</v>
+        <v>81.837</v>
       </c>
       <c r="V2">
-        <v>0.1266756715428921</v>
+        <v>0.2721640227476804</v>
       </c>
       <c r="W2">
-        <v>0.131442000540343</v>
+        <v>0.1599443671766342</v>
       </c>
       <c r="X2">
-        <v>0.02498026850291799</v>
+        <v>0.05021839367146134</v>
       </c>
       <c r="Y2">
-        <v>0.106461732037425</v>
+        <v>0.1097259735051729</v>
       </c>
       <c r="Z2">
-        <v>0.8857497414684593</v>
+        <v>0.3451817901084077</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02390750016951997</v>
+        <v>0.04835309440569568</v>
       </c>
       <c r="AC2">
-        <v>-0.02547298286685868</v>
+        <v>-0.04835309440569568</v>
       </c>
       <c r="AD2">
-        <v>92.86</v>
+        <v>467.286</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>92.86</v>
+        <v>467.286</v>
       </c>
       <c r="AG2">
-        <v>43.155</v>
+        <v>385.449</v>
       </c>
       <c r="AH2">
-        <v>0.1913692193553705</v>
+        <v>0.608464327010219</v>
       </c>
       <c r="AI2">
-        <v>0.5364622148275245</v>
+        <v>0.767943598087068</v>
       </c>
       <c r="AJ2">
-        <v>0.0990850333497882</v>
+        <v>0.5617651816905904</v>
       </c>
       <c r="AK2">
-        <v>0.3497390430497925</v>
+        <v>0.7318841818047177</v>
       </c>
       <c r="AL2">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="AM2">
-        <v>3.336</v>
+        <v>3.699</v>
       </c>
       <c r="AN2">
-        <v>4.186654643823264</v>
+        <v>22.26231538828014</v>
       </c>
       <c r="AO2">
-        <v>5.561307901907357</v>
+        <v>4.51219512195122</v>
       </c>
       <c r="AP2">
-        <v>1.945671776375113</v>
+        <v>18.36345878989995</v>
       </c>
       <c r="AQ2">
-        <v>6.11810551558753</v>
+        <v>5.001351716680184</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NZX Limited (NZSE:NZX)</t>
+          <t>General Capital Limited (NZSE:GEN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,125 +724,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0148</v>
-      </c>
-      <c r="E3">
-        <v>0.112</v>
-      </c>
-      <c r="F3">
-        <v>0.07690000000000001</v>
-      </c>
       <c r="G3">
-        <v>0.3472222222222222</v>
+        <v>0.5747126436781609</v>
       </c>
       <c r="H3">
-        <v>0.3472222222222222</v>
+        <v>0.5747126436781609</v>
       </c>
       <c r="I3">
-        <v>0.3003472222222222</v>
+        <v>0.6568144499178982</v>
       </c>
       <c r="J3">
-        <v>0.2134543151642208</v>
+        <v>0.4577676318635108</v>
       </c>
       <c r="K3">
-        <v>11.3</v>
+        <v>1.15</v>
       </c>
       <c r="L3">
-        <v>0.1961805555555556</v>
+        <v>0.1888341543513957</v>
       </c>
       <c r="M3">
-        <v>9.74</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02801265458728789</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.8619469026548672</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>9.74</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02801265458728789</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.8619469026548672</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>14.9</v>
+        <v>9.77</v>
       </c>
       <c r="V3">
-        <v>0.04285303422490653</v>
+        <v>1.150765606595995</v>
       </c>
       <c r="W3">
-        <v>0.2671394799054374</v>
+        <v>0.1599443671766342</v>
       </c>
       <c r="X3">
-        <v>0.02345186425054933</v>
+        <v>0.04818156146787071</v>
       </c>
       <c r="Y3">
-        <v>0.2436876156548881</v>
-      </c>
-      <c r="Z3">
-        <v>1.443609022556391</v>
-      </c>
-      <c r="AA3">
-        <v>0.3081445752746648</v>
+        <v>0.1117628057087635</v>
       </c>
       <c r="AB3">
-        <v>0.02289845493269947</v>
-      </c>
-      <c r="AC3">
-        <v>0.2852461203419653</v>
+        <v>0.04808407543130452</v>
       </c>
       <c r="AD3">
-        <v>31.6</v>
+        <v>0.059</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>31.6</v>
+        <v>0.059</v>
       </c>
       <c r="AG3">
-        <v>16.7</v>
+        <v>-9.711</v>
       </c>
       <c r="AH3">
-        <v>0.08331136303717374</v>
+        <v>0.006901391975669669</v>
       </c>
       <c r="AI3">
-        <v>0.3954943679599499</v>
+        <v>0.007117867052720473</v>
       </c>
       <c r="AJ3">
-        <v>0.04582875960482987</v>
+        <v>7.953316953316953</v>
       </c>
       <c r="AK3">
-        <v>0.256923076923077</v>
+        <v>6.557056043214045</v>
       </c>
       <c r="AL3">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AM3">
-        <v>1.596</v>
+        <v>2.21</v>
       </c>
       <c r="AN3">
-        <v>1.663157894736842</v>
+        <v>0.01442542787286064</v>
       </c>
       <c r="AO3">
-        <v>8.963730569948186</v>
+        <v>1.809954751131222</v>
       </c>
       <c r="AP3">
-        <v>0.8789473684210528</v>
+        <v>-2.374327628361858</v>
       </c>
       <c r="AQ3">
-        <v>10.83959899749374</v>
+        <v>1.809954751131222</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blackwell Global Holdings Limited (NZSE:BGI)</t>
+          <t>NZX Limited (NZSE:NZX)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,101 +840,125 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0484</v>
+      </c>
+      <c r="E4">
+        <v>0.0172</v>
+      </c>
+      <c r="F4">
+        <v>0.021</v>
+      </c>
       <c r="G4">
-        <v>-0</v>
+        <v>0.3274956217162872</v>
       </c>
       <c r="H4">
-        <v>-0</v>
+        <v>0.3274956217162872</v>
       </c>
       <c r="I4">
-        <v>-0</v>
+        <v>0.2539404553415061</v>
       </c>
       <c r="J4">
-        <v>-0</v>
+        <v>0.1860875656742557</v>
       </c>
       <c r="K4">
-        <v>-0.452</v>
+        <v>9.19</v>
       </c>
       <c r="L4">
-        <v>16.14285714285714</v>
+        <v>0.1609457092819614</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0391880695940348</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.029379760609358</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0391880695940348</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.029379760609358</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.105</v>
+        <v>10.3</v>
       </c>
       <c r="V4">
-        <v>0.06687898089171974</v>
+        <v>0.04266777133388567</v>
       </c>
       <c r="W4">
-        <v>-1.965217391304348</v>
+        <v>0.1902691511387164</v>
       </c>
       <c r="X4">
-        <v>0.02650867275528664</v>
+        <v>0.04904529251947725</v>
       </c>
       <c r="Y4">
-        <v>-1.991726064059634</v>
+        <v>0.1412238586192391</v>
       </c>
       <c r="Z4">
-        <v>-0.07000000000000002</v>
+        <v>1.300683371298406</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.2420410022779043</v>
       </c>
       <c r="AB4">
-        <v>0.02488880074139167</v>
+        <v>0.04725707703101718</v>
       </c>
       <c r="AC4">
-        <v>-0.02488880074139167</v>
+        <v>0.1947839252468872</v>
       </c>
       <c r="AD4">
-        <v>0.993</v>
+        <v>32.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.993</v>
+        <v>32.7</v>
       </c>
       <c r="AG4">
-        <v>0.888</v>
+        <v>22.4</v>
       </c>
       <c r="AH4">
-        <v>0.3874365977370269</v>
+        <v>0.11929952572054</v>
       </c>
       <c r="AI4">
-        <v>1.056382978723404</v>
+        <v>0.3190243902439024</v>
       </c>
       <c r="AJ4">
-        <v>0.3612693246541904</v>
+        <v>0.08491281273692192</v>
       </c>
       <c r="AK4">
-        <v>1.063473053892216</v>
+        <v>0.2429501084598699</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.489</v>
+      </c>
+      <c r="AN4">
+        <v>1.934911242603551</v>
+      </c>
+      <c r="AO4">
+        <v>7.671957671957673</v>
+      </c>
+      <c r="AP4">
+        <v>1.325443786982249</v>
+      </c>
+      <c r="AQ4">
+        <v>9.738079247817328</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geneva Finance Limited (NZSE:GFL)</t>
+          <t>Blackwell Global Holdings Limited (NZSE:BGI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -974,104 +977,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.272</v>
-      </c>
-      <c r="E5">
-        <v>0.0702</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5">
-        <v>4.25</v>
-      </c>
-      <c r="L5">
-        <v>0.1778242677824268</v>
+        <v>-0.193</v>
       </c>
       <c r="M5">
-        <v>1.47</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.03983739837398374</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.3458823529411765</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.47</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03983739837398374</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.3458823529411765</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>24.3</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V5">
-        <v>0.6585365853658537</v>
+        <v>0.3335294117647059</v>
       </c>
       <c r="W5">
-        <v>0.2103960396039604</v>
+        <v>3.641509433962264</v>
       </c>
       <c r="X5">
-        <v>0.03213148535016535</v>
+        <v>0.05021839367146134</v>
       </c>
       <c r="Y5">
-        <v>0.1782645542537951</v>
+        <v>3.591291040290803</v>
       </c>
       <c r="Z5">
-        <v>0.4149305555555555</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02605716499232568</v>
+        <v>0.04835309440569568</v>
       </c>
       <c r="AC5">
-        <v>-0.02605716499232568</v>
+        <v>-0.04835309440569568</v>
       </c>
       <c r="AD5">
-        <v>60.1</v>
+        <v>0.527</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>60.1</v>
+        <v>0.527</v>
       </c>
       <c r="AG5">
-        <v>35.8</v>
+        <v>-0.03999999999999992</v>
       </c>
       <c r="AH5">
-        <v>0.6195876288659794</v>
+        <v>0.2366412213740458</v>
       </c>
       <c r="AI5">
-        <v>0.7078916372202591</v>
+        <v>0.8768718801996673</v>
       </c>
       <c r="AJ5">
-        <v>0.4924346629986245</v>
+        <v>-0.02409638554216863</v>
       </c>
       <c r="AK5">
-        <v>0.5907590759075908</v>
+        <v>-1.176470588235289</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Capital Limited (NZSE:GEN)</t>
+          <t>Geneva Finance Limited (NZSE:GFL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1096,113 +1075,223 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.292</v>
+      </c>
+      <c r="E6">
+        <v>-0.0371</v>
+      </c>
       <c r="G6">
-        <v>0.6028708133971292</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.6028708133971292</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.7440191387559809</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.5058092689671637</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>0.327</v>
+        <v>2.78</v>
       </c>
       <c r="L6">
-        <v>0.07822966507177034</v>
+        <v>0.1153526970954357</v>
       </c>
       <c r="M6">
+        <v>1.48</v>
+      </c>
+      <c r="N6">
+        <v>0.07708333333333334</v>
+      </c>
+      <c r="O6">
+        <v>0.5323741007194245</v>
+      </c>
+      <c r="P6">
+        <v>1.48</v>
+      </c>
+      <c r="Q6">
+        <v>0.07708333333333334</v>
+      </c>
+      <c r="R6">
+        <v>0.5323741007194245</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>22.1</v>
+      </c>
+      <c r="V6">
+        <v>1.151041666666667</v>
+      </c>
+      <c r="W6">
+        <v>0.1177966101694915</v>
+      </c>
+      <c r="X6">
+        <v>0.06423747772623621</v>
+      </c>
+      <c r="Y6">
+        <v>0.0535591324432553</v>
+      </c>
+      <c r="Z6">
+        <v>0.4057239057239057</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.04878551491324747</v>
+      </c>
+      <c r="AC6">
+        <v>-0.04878551491324747</v>
+      </c>
+      <c r="AD6">
+        <v>46</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>46</v>
+      </c>
+      <c r="AG6">
+        <v>23.9</v>
+      </c>
+      <c r="AH6">
+        <v>0.705521472392638</v>
+      </c>
+      <c r="AI6">
+        <v>0.6715328467153284</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5545243619489559</v>
+      </c>
+      <c r="AK6">
+        <v>0.5150862068965517</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Harmoney Corp Limited (ASX:HMY)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0.1698412698412698</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-12.6</v>
+      </c>
+      <c r="L7">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="M7">
         <v>-0</v>
       </c>
-      <c r="N6">
+      <c r="N7">
         <v>-0</v>
       </c>
-      <c r="O6">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>-0</v>
       </c>
-      <c r="P6">
+      <c r="Q7">
         <v>-0</v>
       </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>10.4</v>
-      </c>
-      <c r="V6">
-        <v>1.674718196457327</v>
-      </c>
-      <c r="W6">
-        <v>0.05248796147672552</v>
-      </c>
-      <c r="X6">
-        <v>0.02309069858995959</v>
-      </c>
-      <c r="Y6">
-        <v>0.02939726288676592</v>
-      </c>
-      <c r="Z6">
-        <v>-3.483333333333335</v>
-      </c>
-      <c r="AA6">
-        <v>-1.761902286902288</v>
-      </c>
-      <c r="AB6">
-        <v>0.02292619959764827</v>
-      </c>
-      <c r="AC6">
-        <v>-1.784828486499936</v>
-      </c>
-      <c r="AD6">
-        <v>0.167</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0.167</v>
-      </c>
-      <c r="AG6">
-        <v>-10.233</v>
-      </c>
-      <c r="AH6">
-        <v>0.02618786263133135</v>
-      </c>
-      <c r="AI6">
-        <v>0.02269946989261927</v>
-      </c>
-      <c r="AJ6">
-        <v>2.543624161073825</v>
-      </c>
-      <c r="AK6">
-        <v>3.362799868550772</v>
-      </c>
-      <c r="AL6">
-        <v>1.74</v>
-      </c>
-      <c r="AM6">
-        <v>1.74</v>
-      </c>
-      <c r="AN6">
-        <v>0.05251572327044025</v>
-      </c>
-      <c r="AO6">
-        <v>1.78735632183908</v>
-      </c>
-      <c r="AP6">
-        <v>-3.217924528301887</v>
-      </c>
-      <c r="AQ6">
-        <v>1.78735632183908</v>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>39.1</v>
+      </c>
+      <c r="V7">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="W7">
+        <v>-0.2386363636363636</v>
+      </c>
+      <c r="X7">
+        <v>0.1353517395798326</v>
+      </c>
+      <c r="Y7">
+        <v>-0.3739881032161962</v>
+      </c>
+      <c r="Z7">
+        <v>0.09287469287469288</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.04899111034562573</v>
+      </c>
+      <c r="AC7">
+        <v>-0.04899111034562573</v>
+      </c>
+      <c r="AD7">
+        <v>388</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>388</v>
+      </c>
+      <c r="AG7">
+        <v>348.9</v>
+      </c>
+      <c r="AH7">
+        <v>0.9284517827231396</v>
+      </c>
+      <c r="AI7">
+        <v>0.9052729818012132</v>
+      </c>
+      <c r="AJ7">
+        <v>0.9210665258711722</v>
+      </c>
+      <c r="AK7">
+        <v>0.8957637997432605</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1702</v>
+        <v>0.14965</v>
       </c>
       <c r="E2">
-        <v>-0.009950000000000001</v>
+        <v>0.0399</v>
       </c>
       <c r="F2">
-        <v>0.021</v>
+        <v>0.114</v>
       </c>
       <c r="G2">
-        <v>0.2392880685563613</v>
+        <v>0.1712877803466257</v>
       </c>
       <c r="H2">
-        <v>0.2090592334494774</v>
+        <v>0.1464243324276738</v>
       </c>
       <c r="I2">
-        <v>0.1742160278745645</v>
+        <v>0.1676313909467799</v>
       </c>
       <c r="J2">
-        <v>0.1435084080724074</v>
+        <v>0.1479584992945939</v>
       </c>
       <c r="K2">
-        <v>0.3269999999999996</v>
+        <v>-5.123</v>
       </c>
       <c r="L2">
-        <v>0.00307938600621527</v>
+        <v>-0.02881797368524675</v>
       </c>
       <c r="M2">
-        <v>10.94</v>
+        <v>13.69</v>
       </c>
       <c r="N2">
-        <v>0.03638298579932821</v>
+        <v>0.02384145173368628</v>
       </c>
       <c r="O2">
-        <v>33.45565749235479</v>
+        <v>-2.672262346281475</v>
       </c>
       <c r="P2">
-        <v>10.94</v>
+        <v>13.69</v>
       </c>
       <c r="Q2">
-        <v>0.03638298579932821</v>
+        <v>0.02384145173368628</v>
       </c>
       <c r="R2">
-        <v>33.45565749235479</v>
+        <v>-2.672262346281475</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>81.837</v>
+        <v>66.54299999999999</v>
       </c>
       <c r="V2">
-        <v>0.2721640227476804</v>
+        <v>0.1158861740478222</v>
       </c>
       <c r="W2">
-        <v>0.1599443671766342</v>
+        <v>-0.02471443406022845</v>
       </c>
       <c r="X2">
-        <v>0.05021839367146134</v>
+        <v>0.05547760712132675</v>
       </c>
       <c r="Y2">
-        <v>0.1097259735051729</v>
+        <v>-0.08019204118155521</v>
       </c>
       <c r="Z2">
-        <v>0.3451817901084077</v>
+        <v>0.2458738867827451</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.02219674916919303</v>
       </c>
       <c r="AB2">
-        <v>0.04835309440569568</v>
+        <v>0.04648922131101357</v>
       </c>
       <c r="AC2">
-        <v>-0.04835309440569568</v>
+        <v>-0.02131851708129808</v>
       </c>
       <c r="AD2">
-        <v>467.286</v>
+        <v>689.986</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>467.286</v>
+        <v>689.986</v>
       </c>
       <c r="AG2">
-        <v>385.449</v>
+        <v>623.443</v>
       </c>
       <c r="AH2">
-        <v>0.608464327010219</v>
+        <v>0.5457903679492737</v>
       </c>
       <c r="AI2">
-        <v>0.767943598087068</v>
+        <v>0.7032356631290138</v>
       </c>
       <c r="AJ2">
-        <v>0.5617651816905904</v>
+        <v>0.5205539501007387</v>
       </c>
       <c r="AK2">
-        <v>0.7318841818047177</v>
+        <v>0.6816445371609506</v>
       </c>
       <c r="AL2">
-        <v>4.1</v>
+        <v>8.071999999999999</v>
       </c>
       <c r="AM2">
-        <v>3.699</v>
+        <v>5.531999999999999</v>
       </c>
       <c r="AN2">
-        <v>22.26231538828014</v>
+        <v>24.81964028776979</v>
       </c>
       <c r="AO2">
-        <v>4.51219512195122</v>
+        <v>3.69177403369673</v>
       </c>
       <c r="AP2">
-        <v>18.36345878989995</v>
+        <v>22.4260071942446</v>
       </c>
       <c r="AQ2">
-        <v>5.001351716680184</v>
+        <v>5.386840202458425</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Capital Limited (NZSE:GEN)</t>
+          <t>Smartpay Holdings Limited (NZSE:SPY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,23 +724,29 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.345</v>
+      </c>
+      <c r="E3">
+        <v>0.323</v>
+      </c>
       <c r="G3">
-        <v>0.5747126436781609</v>
+        <v>0.1793296089385475</v>
       </c>
       <c r="H3">
-        <v>0.5747126436781609</v>
+        <v>0.1793296089385475</v>
       </c>
       <c r="I3">
-        <v>0.6568144499178982</v>
+        <v>0.1148975791433892</v>
       </c>
       <c r="J3">
-        <v>0.4577676318635108</v>
+        <v>0.1070053970926398</v>
       </c>
       <c r="K3">
-        <v>1.15</v>
+        <v>4.76</v>
       </c>
       <c r="L3">
-        <v>0.1888341543513957</v>
+        <v>0.08864059590316573</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,64 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.77</v>
+        <v>11.5</v>
       </c>
       <c r="V3">
-        <v>1.150765606595995</v>
+        <v>0.05122494432071269</v>
       </c>
       <c r="W3">
-        <v>0.1599443671766342</v>
+        <v>0.2096916299559471</v>
       </c>
       <c r="X3">
-        <v>0.04818156146787071</v>
+        <v>0.05014080355653328</v>
       </c>
       <c r="Y3">
-        <v>0.1117628057087635</v>
+        <v>0.1595508263994139</v>
+      </c>
+      <c r="Z3">
+        <v>3.608870967741936</v>
+      </c>
+      <c r="AA3">
+        <v>0.386168670959325</v>
       </c>
       <c r="AB3">
-        <v>0.04808407543130452</v>
+        <v>0.04961058501430163</v>
+      </c>
+      <c r="AC3">
+        <v>0.3365580859450233</v>
       </c>
       <c r="AD3">
-        <v>0.059</v>
+        <v>9.16</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.059</v>
+        <v>9.16</v>
       </c>
       <c r="AG3">
-        <v>-9.711</v>
+        <v>-2.34</v>
       </c>
       <c r="AH3">
-        <v>0.006901391975669669</v>
+        <v>0.03920225969357186</v>
       </c>
       <c r="AI3">
-        <v>0.007117867052720473</v>
+        <v>0.2491838955386289</v>
       </c>
       <c r="AJ3">
-        <v>7.953316953316953</v>
+        <v>-0.01053294922578322</v>
       </c>
       <c r="AK3">
-        <v>6.557056043214045</v>
+        <v>-0.09263657957244655</v>
       </c>
       <c r="AL3">
-        <v>2.21</v>
+        <v>0.822</v>
       </c>
       <c r="AM3">
-        <v>2.21</v>
+        <v>0.452</v>
       </c>
       <c r="AN3">
-        <v>0.01442542787286064</v>
+        <v>0.906930693069307</v>
       </c>
       <c r="AO3">
-        <v>1.809954751131222</v>
+        <v>7.506082725060828</v>
       </c>
       <c r="AP3">
-        <v>-2.374327628361858</v>
+        <v>-0.2316831683168317</v>
       </c>
       <c r="AQ3">
-        <v>1.809954751131222</v>
+        <v>13.65044247787611</v>
       </c>
     </row>
     <row r="4">
@@ -841,49 +856,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0484</v>
+        <v>0.0883</v>
       </c>
       <c r="E4">
-        <v>0.0172</v>
+        <v>0.0399</v>
       </c>
       <c r="F4">
-        <v>0.021</v>
+        <v>0.114</v>
       </c>
       <c r="G4">
-        <v>0.3274956217162872</v>
+        <v>0.2586750788643533</v>
       </c>
       <c r="H4">
-        <v>0.3274956217162872</v>
+        <v>0.2586750788643533</v>
       </c>
       <c r="I4">
-        <v>0.2539404553415061</v>
+        <v>0.2334384858044164</v>
       </c>
       <c r="J4">
-        <v>0.1860875656742557</v>
+        <v>0.1592316175527686</v>
       </c>
       <c r="K4">
-        <v>9.19</v>
+        <v>8.42</v>
       </c>
       <c r="L4">
-        <v>0.1609457092819614</v>
+        <v>0.132807570977918</v>
       </c>
       <c r="M4">
-        <v>9.460000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="N4">
-        <v>0.0391880695940348</v>
+        <v>0.04387846291331546</v>
       </c>
       <c r="O4">
-        <v>1.029379760609358</v>
+        <v>1.166270783847981</v>
       </c>
       <c r="P4">
-        <v>9.460000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="Q4">
-        <v>0.0391880695940348</v>
+        <v>0.04387846291331546</v>
       </c>
       <c r="R4">
-        <v>1.029379760609358</v>
+        <v>1.166270783847981</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,73 +907,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>10.3</v>
+        <v>7.66</v>
       </c>
       <c r="V4">
-        <v>0.04266777133388567</v>
+        <v>0.03422698838248436</v>
       </c>
       <c r="W4">
-        <v>0.1902691511387164</v>
+        <v>0.1206303724928367</v>
       </c>
       <c r="X4">
-        <v>0.04904529251947725</v>
+        <v>0.05159997846121348</v>
       </c>
       <c r="Y4">
-        <v>0.1412238586192391</v>
+        <v>0.0690303940316232</v>
       </c>
       <c r="Z4">
-        <v>1.300683371298406</v>
+        <v>0.8637602179836511</v>
       </c>
       <c r="AA4">
-        <v>0.2420410022779043</v>
+        <v>0.1375379366872688</v>
       </c>
       <c r="AB4">
-        <v>0.04725707703101718</v>
+        <v>0.0480822782474264</v>
       </c>
       <c r="AC4">
-        <v>0.1947839252468872</v>
+        <v>0.08945565843984236</v>
       </c>
       <c r="AD4">
-        <v>32.7</v>
+        <v>50.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>32.7</v>
+        <v>50.3</v>
       </c>
       <c r="AG4">
-        <v>22.4</v>
+        <v>42.64</v>
       </c>
       <c r="AH4">
-        <v>0.11929952572054</v>
+        <v>0.1835096680043779</v>
       </c>
       <c r="AI4">
-        <v>0.3190243902439024</v>
+        <v>0.4089430894308943</v>
       </c>
       <c r="AJ4">
-        <v>0.08491281273692192</v>
+        <v>0.1600360306260321</v>
       </c>
       <c r="AK4">
-        <v>0.2429501084598699</v>
+        <v>0.3696896133171493</v>
       </c>
       <c r="AL4">
-        <v>1.89</v>
+        <v>2.59</v>
       </c>
       <c r="AM4">
-        <v>1.489</v>
+        <v>1.57</v>
       </c>
       <c r="AN4">
-        <v>1.934911242603551</v>
+        <v>2.84180790960452</v>
       </c>
       <c r="AO4">
-        <v>7.671957671957673</v>
+        <v>5.714285714285715</v>
       </c>
       <c r="AP4">
-        <v>1.325443786982249</v>
+        <v>2.409039548022599</v>
       </c>
       <c r="AQ4">
-        <v>9.738079247817328</v>
+        <v>9.426751592356689</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blackwell Global Holdings Limited (NZSE:BGI)</t>
+          <t>New Zealand Rural Land Company Limited (NZSE:NZL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,86 +992,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1.067714631197098</v>
+      </c>
+      <c r="J5">
+        <v>1.067714631197098</v>
+      </c>
       <c r="K5">
-        <v>-0.193</v>
+        <v>-14.4</v>
+      </c>
+      <c r="L5">
+        <v>-1.741233373639661</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>2.63</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03549257759784076</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0.1826388888888889</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2.63</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03549257759784076</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0.1826388888888889</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0.5669999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="V5">
-        <v>0.3335294117647059</v>
+        <v>0.001889338731443995</v>
       </c>
       <c r="W5">
-        <v>3.641509433962264</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="X5">
-        <v>0.05021839367146134</v>
+        <v>0.05935523578144002</v>
       </c>
       <c r="Y5">
-        <v>3.591291040290803</v>
+        <v>-0.1704663468925511</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.04157805563515884</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.04439349833838605</v>
       </c>
       <c r="AB5">
-        <v>0.04835309440569568</v>
+        <v>0.04465576904047001</v>
       </c>
       <c r="AC5">
-        <v>-0.04835309440569568</v>
+        <v>-0.0002622707020839624</v>
       </c>
       <c r="AD5">
-        <v>0.527</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.527</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AG5">
-        <v>-0.03999999999999992</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.2366412213740458</v>
+        <v>0.5459558823529411</v>
       </c>
       <c r="AI5">
-        <v>0.8768718801996673</v>
+        <v>0.4040816326530612</v>
       </c>
       <c r="AJ5">
-        <v>-0.02409638554216863</v>
+        <v>0.5455660493070035</v>
       </c>
       <c r="AK5">
-        <v>-1.176470588235289</v>
+        <v>0.4037030314031584</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>3.51</v>
+      </c>
+      <c r="AO5">
+        <v>1.894849785407725</v>
+      </c>
+      <c r="AQ5">
+        <v>2.515669515669515</v>
       </c>
     </row>
     <row r="6">
@@ -1076,10 +1115,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.292</v>
+        <v>0.211</v>
       </c>
       <c r="E6">
-        <v>-0.0371</v>
+        <v>-0.157</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1133,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>2.78</v>
+        <v>1.32</v>
       </c>
       <c r="L6">
-        <v>0.1153526970954357</v>
+        <v>0.04474576271186441</v>
       </c>
       <c r="M6">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="N6">
-        <v>0.07708333333333334</v>
+        <v>0.0775</v>
       </c>
       <c r="O6">
-        <v>0.5323741007194245</v>
+        <v>0.9393939393939393</v>
       </c>
       <c r="P6">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>0.07708333333333334</v>
+        <v>0.0775</v>
       </c>
       <c r="R6">
-        <v>0.5323741007194245</v>
+        <v>0.9393939393939393</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1163,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>22.1</v>
+        <v>17.9</v>
       </c>
       <c r="V6">
-        <v>1.151041666666667</v>
+        <v>1.11875</v>
       </c>
       <c r="W6">
-        <v>0.1177966101694915</v>
+        <v>0.06168224299065421</v>
       </c>
       <c r="X6">
-        <v>0.06423747772623621</v>
+        <v>0.07916683626440732</v>
       </c>
       <c r="Y6">
-        <v>0.0535591324432553</v>
+        <v>-0.01748459327375311</v>
       </c>
       <c r="Z6">
-        <v>0.4057239057239057</v>
+        <v>0.65121412803532</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04878551491324747</v>
+        <v>0.04237476346051219</v>
       </c>
       <c r="AC6">
-        <v>-0.04878551491324747</v>
+        <v>-0.04237476346051219</v>
       </c>
       <c r="AD6">
-        <v>46</v>
+        <v>59.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>46</v>
+        <v>59.2</v>
       </c>
       <c r="AG6">
-        <v>23.9</v>
+        <v>41.3</v>
       </c>
       <c r="AH6">
-        <v>0.705521472392638</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="AI6">
-        <v>0.6715328467153284</v>
+        <v>0.7158403869407497</v>
       </c>
       <c r="AJ6">
-        <v>0.5545243619489559</v>
+        <v>0.7207678883071553</v>
       </c>
       <c r="AK6">
-        <v>0.5150862068965517</v>
+        <v>0.6373456790123456</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1237,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.1698412698412698</v>
+        <v>0.1930131004366812</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1210,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-12.6</v>
+        <v>-5.05</v>
       </c>
       <c r="L7">
-        <v>-0.6666666666666667</v>
+        <v>-0.2205240174672489</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1237,60 +1276,176 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>39.1</v>
+        <v>28.9</v>
       </c>
       <c r="V7">
-        <v>1.307692307692308</v>
+        <v>0.847507331378299</v>
       </c>
       <c r="W7">
-        <v>-0.2386363636363636</v>
+        <v>-0.1240786240786241</v>
       </c>
       <c r="X7">
-        <v>0.1353517395798326</v>
+        <v>0.1619168087182987</v>
       </c>
       <c r="Y7">
-        <v>-0.3739881032161962</v>
+        <v>-0.2859954327969228</v>
       </c>
       <c r="Z7">
-        <v>0.09287469287469288</v>
+        <v>0.05864276568501921</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04899111034562573</v>
+        <v>0.04489616437460075</v>
       </c>
       <c r="AC7">
-        <v>-0.04899111034562573</v>
+        <v>-0.04489616437460075</v>
       </c>
       <c r="AD7">
-        <v>388</v>
+        <v>481.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>388</v>
+        <v>481.9</v>
       </c>
       <c r="AG7">
-        <v>348.9</v>
+        <v>453</v>
       </c>
       <c r="AH7">
-        <v>0.9284517827231396</v>
+        <v>0.9339147286821705</v>
       </c>
       <c r="AI7">
-        <v>0.9052729818012132</v>
+        <v>0.930847981456442</v>
       </c>
       <c r="AJ7">
-        <v>0.9210665258711722</v>
+        <v>0.9299938411003901</v>
       </c>
       <c r="AK7">
-        <v>0.8957637997432605</v>
+        <v>0.926759410801964</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Blackwell Global Holdings Limited (NZSE:BGI)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.722</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-0.173</v>
+      </c>
+      <c r="L8">
+        <v>-173</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0.443</v>
+      </c>
+      <c r="V8">
+        <v>0.2590643274853801</v>
+      </c>
+      <c r="W8">
+        <v>-2.337837837837838</v>
+      </c>
+      <c r="X8">
+        <v>0.05132939838544751</v>
+      </c>
+      <c r="Y8">
+        <v>-2.389167236223285</v>
+      </c>
+      <c r="Z8">
+        <v>0.02941176470588233</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.04928115153198194</v>
+      </c>
+      <c r="AC8">
+        <v>-0.04928115153198194</v>
+      </c>
+      <c r="AD8">
+        <v>0.326</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0.326</v>
+      </c>
+      <c r="AG8">
+        <v>-0.117</v>
+      </c>
+      <c r="AH8">
+        <v>0.1601178781925344</v>
+      </c>
+      <c r="AI8">
+        <v>0.6533066132264529</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.07344632768361582</v>
+      </c>
+      <c r="AK8">
+        <v>-2.089285714285714</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
